--- a/小红书笔记数据.xlsx
+++ b/小红书笔记数据.xlsx
@@ -435,92 +435,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="15"/>
+    <col customWidth="1" max="1" min="1" width="6"/>
     <col customWidth="1" max="2" min="2" width="9"/>
-    <col customWidth="1" max="3" min="3" width="28"/>
-    <col customWidth="1" max="4" min="4" width="33"/>
+    <col customWidth="1" max="3" min="3" width="15"/>
+    <col customWidth="1" max="4" min="4" width="9"/>
     <col customWidth="1" max="5" min="5" width="28"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="7"/>
-    <col customWidth="1" max="8" min="8" width="7"/>
-    <col customWidth="1" max="9" min="9" width="10"/>
+    <col customWidth="1" max="6" min="6" width="33"/>
+    <col customWidth="1" max="7" min="7" width="28"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="7"/>
     <col customWidth="1" max="10" min="10" width="7"/>
-    <col customWidth="1" max="11" min="11" width="7"/>
+    <col customWidth="1" max="11" min="11" width="10"/>
     <col customWidth="1" max="12" min="12" width="7"/>
     <col customWidth="1" max="13" min="13" width="7"/>
-    <col customWidth="1" max="14" min="14" width="50"/>
+    <col customWidth="1" max="14" min="14" width="7"/>
+    <col customWidth="1" max="15" min="15" width="7"/>
+    <col customWidth="1" max="16" min="16" width="50"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="25" r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>小红书号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>用户昵称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>笔记标题</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>笔记ID</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>发布日期</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>关注数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>粉丝数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>获赞与收藏数</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>收藏数</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>评论数</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>分享数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>点赞数</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>笔记链接</t>
         </is>
@@ -529,1224 +541,1032 @@
     <row customHeight="1" ht="20" r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Python爬虫真正的高阶玩法🔥</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>69fe0ce500000000360330d3</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0ce500000000360330d3?xsec_token=ABqlStnkjRyzBtQg4E4K66p3c1K-Mr-pT1Hw1_b_BuRcc=</t>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fe0ce500000000360330d3?xsec_token=AB-XGVDyTWQ2dKewBkTJsfeoGUnvCOSq5j6B726lmyMq4=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Python自动化实战｜发票PDF批量下载+自动重</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>69fe0b45000000003803582b</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0b45000000003803582b?xsec_token=ABqlStnkjRyzBtQg4E4K66p6r8umETNGWJGQ05CAlbTpw=</t>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fe0b45000000003803582b?xsec_token=AB-XGVDyTWQ2dKewBkTJsfeiT0eVYZ45fjgRuNHYc25Gw=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Python自动化｜普通人也能用的8大场景✅</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>69fe0aca00000000360329cf</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0aca00000000360329cf?xsec_token=ABqlStnkjRyzBtQg4E4K66pxGSLi7hXodfPOH7ogU-teQ=</t>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fe0aca00000000360329cf?xsec_token=AB-XGVDyTWQ2dKewBkTJsfektepVTj2ENx8r66s1lUj3k=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Python后端框架选型｜一篇搞定✅</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>69fe0a3a000000003601f547</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0a3a000000003601f547?xsec_token=ABqlStnkjRyzBtQg4E4K66p5qd8xFUxpWawj9q8la45Nk=</t>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fe0a3a000000003601f547?xsec_token=AB-XGVDyTWQ2dKewBkTJsfelGYXhDZVjAiBpw7jPlcAIQ=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>职场逆袭｜Python搞定所有无脑重复工作</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>69fcc51700000000380342ab</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fcc51700000000380342ab?xsec_token=ABxYO3edZ5UtDbWiemxd10E7Q7YiN0FojDdUjXkHko6Is=</t>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fcc51700000000380342ab?xsec_token=AB-w4DjPUYQJStSYryP2oTEhoPqEhPaiwj6i-cHxKcRz4=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>职场开挂🔥RPA+AI+Python终结无脑重复工作</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>69fcc1a6000000003701e698</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fcc1a6000000003701e698?xsec_token=ABxYO3edZ5UtDbWiemxd10E9M8K5KyQENA1pM9g9TCaqw=</t>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fcc1a6000000003701e698?xsec_token=AB-w4DjPUYQJStSYryP2oTEin9SpHNblmPMJS5VzTJZQ0=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>抖音孵化器运营封神！RPA+爬虫直接把数据效</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>69fc22b9000000003700d460</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc22b9000000003700d460?xsec_token=ABxYO3edZ5UtDbWiemxd10EyHcjgkP363FOqgDTKopFIQ=</t>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc22b9000000003700d460?xsec_token=AB-w4DjPUYQJStSYryP2oTEsurYUGKPI-MXQPhOyBbYFg=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>别卷了！RPA+Python+Agent，打工人的AI效率</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>69fb6715000000003700fbec</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fb6715000000003700fbec?xsec_token=ABulN_MGrcHFljvp6T8qq-pymsnQXLLB50X1HTpQPCGnY=</t>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fb6715000000003700fbec?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwSZWpuWl4I1VJlylyGjuDQ=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>财务人必看！AI+RPA不是取代你，是帮你把加</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>69fb61190000000036033051</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fb61190000000036033051?xsec_token=ABulN_MGrcHFljvp6T8qq-pxbqlU9kKP680Gb2wfbdmmE=</t>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fb61190000000036033051?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwtmSjAnT9cPAPXmG0txono=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>打工人直接抄！50个RPA核心场景，把重复活</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>69fb5cf500000000380237d4</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fb5cf500000000380237d4?xsec_token=ABulN_MGrcHFljvp6T8qq-p0o9A7bKC6Q6GHtdVJIfUQM=</t>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fb5cf500000000380237d4?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjzh35rSOJD0u2lfPrvRnkqc=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>坐标苏州｜183 慢热男生 真诚找双向奔赴</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>69f94da9000000003701c313</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>电商数据采集天花板：RPA+Python爬虫，规避</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>69f6a411000000003601f0e5</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f94da9000000003701c313?xsec_token=ABlBMKQJhGoj__7-WOt1OJGd9SiSq_OU8Ja5O-HgJitdQ=</t>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69f6a411000000003601f0e5?xsec_token=ABMbRwbRmouOxCyr3Qw4rO5jJbmKwPCEwe_GxOHe3Fu6A=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>电商数据采集天花板：RPA+Python爬虫，规避</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69f6a411000000003601f0e5</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>干货｜爬虫/数据采集/RPA 优缺点彻底讲明白</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>69f574d000000000380376f7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f6a411000000003601f0e5?xsec_token=ABqCM7ahjybfRNYlpzT3zy-l8aBcJKHe6wO_hjb0TL9pk=</t>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69f574d000000000380376f7?xsec_token=ABQpezNZs-QyvSSCcw0Y1eou5yePWNcH51LhhKy6Z677o=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>干货｜爬虫/数据采集/RPA 优缺点彻底讲明白</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69f574d000000000380376f7</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Python自动化 </t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69f573c00000000036033f13</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f574d000000000380376f7?xsec_token=ABNQbNHgy87zezBkD43utIUbZoKDYrMzRovgaxZgkmqow=</t>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69f573c00000000036033f13?xsec_token=ABQpezNZs-QyvSSCcw0Y1eoqQPYPnn7GdIdOODskKVeiU=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>钟帅</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>18113</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>94772868080</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>飞奔的蜗牛</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>66954e05000000000303191d</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Python自动化 </t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69f573c00000000036033f13</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>影刀RPA和Python有什么区别？</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>69f56c37000000003703536f</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f573c00000000036033f13?xsec_token=ABNQbNHgy87zezBkD43utIUXhMJ6QSGXn7A10rHwjwCjM=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>94772868080</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>飞奔的蜗牛</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>66954e05000000000303191d</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">我在追觅写爬虫🦎 </t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69f572bb0000000037037878</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f572bb0000000037037878?xsec_token=ABNQbNHgy87zezBkD43utIUcBXuo6aie_BjLPA0yvRIPc=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>94772868080</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>飞奔的蜗牛</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>66954e05000000000303191d</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>RPA+Python爬虫，我在追觅的高效日常</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>69f56fa2000000003701fae3</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f56fa2000000003701fae3?xsec_token=ABNQbNHgy87zezBkD43utIUZsHhdEwvp-uM08pLBuWAoQ=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>94772868080</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>飞奔的蜗牛</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>66954e05000000000303191d</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>影刀RPA和Python有什么区别？</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>69f56c37000000003703536f</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69f56c37000000003703536f?xsec_token=ABNQbNHgy87zezBkD43utIUcJsVLo0zOYsiJy1GeY4JYI=</t>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69f56c37000000003703536f?xsec_token=ABQpezNZs-QyvSSCcw0Y1eojM0gN8T23DGO7q8kyZF5E8=</t>
         </is>
       </c>
     </row>

--- a/小红书笔记数据.xlsx
+++ b/小红书笔记数据.xlsx
@@ -435,19 +435,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="6"/>
+    <col customWidth="1" max="1" min="1" width="7"/>
     <col customWidth="1" max="2" min="2" width="9"/>
     <col customWidth="1" max="3" min="3" width="15"/>
-    <col customWidth="1" max="4" min="4" width="9"/>
+    <col customWidth="1" max="4" min="4" width="11"/>
     <col customWidth="1" max="5" min="5" width="28"/>
-    <col customWidth="1" max="6" min="6" width="33"/>
+    <col customWidth="1" max="6" min="6" width="44"/>
     <col customWidth="1" max="7" min="7" width="28"/>
     <col customWidth="1" max="8" min="8" width="14"/>
     <col customWidth="1" max="9" min="9" width="7"/>
-    <col customWidth="1" max="10" min="10" width="7"/>
+    <col customWidth="1" max="10" min="10" width="9"/>
     <col customWidth="1" max="11" min="11" width="10"/>
     <col customWidth="1" max="12" min="12" width="7"/>
     <col customWidth="1" max="13" min="13" width="7"/>
@@ -1570,6 +1570,2310 @@
         </is>
       </c>
     </row>
+    <row customHeight="1" ht="20" r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>实话跟你们说，我偷偷在尝试返老还童呢～追觅冰箱 追觅科技 追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6a03e9130000000007028c29</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6a03e9130000000007028c29?xsec_token=ABU1N92RnvLngqUT7UARicyLgy5TOu0wvWCot1_lNHtY8=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>无按键一体式机身，从根源上就很难进水藏污，耐用度直接翻倍。追觅科技 追觅牙刷 追</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69ff0ca9000000001f006720</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69ff0ca9000000001f006720?xsec_token=ABX36zBj4jMIO4gcay5g-dVpMMt6309gyISPo5MLleSMA=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>给大家安利一款我真的超爱的好物 ——无按键智能电动牙刷！追觅 追觅牙刷 追觅科技</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>69ff0c500000000023005e0a</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69ff0c500000000023005e0a?xsec_token=ABX36zBj4jMIO4gcay5g-dVnFDpdZYSTemSBhVbB1Z7js=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>哇也太高效了吧, 反馈处理速度好快，合适的衣服就安排到位了追觅 追觅科技</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>69ff0c2a000000001f00646d</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69ff0c2a000000001f00646d?xsec_token=ABX36zBj4jMIO4gcay5g-dVixMbViuOIUZ-A7V7K4chL0=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>我的减肥效果必须碾压李飞 追觅 追觅科技常新伟 @李飞</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>69fea00a000000001a02fd3d</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fea00a000000001a02fd3d?xsec_token=AB-XGVDyTWQ2dKewBkTJsfehmZY_Ecb39vsqQmtpxUHT0=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>同事也太贴心了一早把新工服备好放桌上，颜值看着确实超好看～追觅 追觅科技 追觅科</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>69fe9f9a0000000023017028</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fe9f9a0000000023017028?xsec_token=AB-XGVDyTWQ2dKewBkTJsfei9vdlNqNGzWrtPFh1-gFwg=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>能当上追觅全球总裁，秘诀就两个：战略 + 顶尖核心技术追觅 追觅科技 追觅科技常</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>69fda9080000000022028a0a</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fda9080000000022028a0a?xsec_token=ABWUaXO9siv7J8CIOSOTmh2_z50-DPvfhSBytyfcp4k6U=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>我没俞总那般坎坷低谷，却听过父母当年为 5 块钱买不起药的往事追觅科技常新伟 追</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>69fda8e00000000023014bd4</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fda8e00000000023014bd4?xsec_token=ABWUaXO9siv7J8CIOSOTmh29eSp6YqZrI9pE79Hr_V5gQ=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>老家北京密云，从小进城叫上北京，妥妥小镇做题家追觅 追觅科技常新伟 北京</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>69fda8b6000000001f004f71</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fda8b6000000001f004f71?xsec_token=ABWUaXO9siv7J8CIOSOTmh23uCDhmer7S9PC6Qo_XEZTM=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>被问怎么考上清华、当上追觅总裁？我其实就是北京密云小镇做题家追觅科技 追觅 追觅</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>69fda89f0000000022025b1a</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fda89f0000000022025b1a?xsec_token=ABWUaXO9siv7J8CIOSOTmh29iqEYAuB-G9FKACzvc-W14=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2015年夏天一个闷热的晚上，实验室太无聊了。我打电话给俞老板：俞师兄，我不想努</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>69fd58d9000000001f0012c0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd58d9000000001f0012c0?xsec_token=ABWUaXO9siv7J8CIOSOTmh27BJXWjf73PqdDOBRUuVsqc=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>俞老板是不是知道我特喜欢《海贼王》，当时就被震撼了：改变世界的梦想，原来真能一直</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>69fd58a9000000002300418f</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd58a9000000002300418f?xsec_token=ABWUaXO9siv7J8CIOSOTmh26F_qqwyouN2y-iSKVmRkSo=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>好多人问我怎么被“忽悠”进追觅的，许知远也问过。其实特简单：俞老板说，走，去自动</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>69fd58650000000023014179</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd58650000000023014179?xsec_token=ABWUaXO9siv7J8CIOSOTmh28ldfbzPvS8VX_vOpMV53dI=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当时我刚入学，幼小心灵受到一点震撼：清华压力这么大吗？脑子都这么疯狂？追觅科技 </t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>69fd580b000000001e00ccd1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd580b000000001e00ccd1?xsec_token=ABWUaXO9siv7J8CIOSOTmh24CHeZn6a1zKBmj3kuKKY54=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>俞老板在迎新演讲上说，研究生阶段他要冲到校学生会去，带领航院成为清华最强的院系。</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>69fd57f10000000020038239</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd57f10000000020038239?xsec_token=ABWUaXO9siv7J8CIOSOTmh2zBIqCuQI4Wcp2ssEu0K7x0=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>我08年清华入学，黑话叫“八字班”。俞老板是“五字班”。第一次见他，是他给航院新</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>69fd577b000000002202b990</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd577b000000002202b990?xsec_token=ABWUaXO9siv7J8CIOSOTmh25QeOVTsGjj1EDYbgIxkV-c=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>网友问我是不是比俞老板小3岁、是不是真90后？是真的。但凡眼神好使的，都能看出我</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>69fd5674000000001a02c5cc</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd5674000000001a02c5cc?xsec_token=ABWUaXO9siv7J8CIOSOTmh24NOYd7MqCjcNIaS2mq0-ls=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>叫醒我的不是梦想，是整夜在想：前摄上2亿像素行不行？让大家拍出更好看的自己。你们</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>69fd5640000000002301df58</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd5640000000002301df58?xsec_token=ABWUaXO9siv7J8CIOSOTmh2xQ8kgKvB-JNhdcEaki-sdk=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>想做成事，就把它具象化。比如要超过乔布斯，就把乔布斯放桌上，日思夜想</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>69fd3edc000000001a035bd8</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fd3edc000000001a035bd8?xsec_token=ABWUaXO9siv7J8CIOSOTmh2_KbzdGIrD9MHnEXCz57uig=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>这个也是非常有意义的，而且我喜欢的一个玩偶，这个是乔布斯的玩偶，这个是我们三四年</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>69fc8c530000000036001927</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc8c530000000036001927?xsec_token=AB-w4DjPUYQJStSYryP2oTEsz8U1yjgWyWu6Yv2baqrsk=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>DREAM BOY，我特别喜欢的小玩偶。愿我一直保持好奇、敢于冒险，永远做世界的</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>69fc8a09000000001a035e51</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc8a09000000001a035e51?xsec_token=AB-w4DjPUYQJStSYryP2oTEo-xwJ4VwN-brufegC2pMJc=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>看看追觅全球总裁桌上最新的小摆件，是沃兹先生亲手送给我的。</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>69fc89b4000000001a02d713</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc89b4000000001a02d713?xsec_token=AB-w4DjPUYQJStSYryP2oTErcpOHsPNxsV4b-UaVHyd_U=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>微米级养护精华，滋养头发和头皮。但对我来说，养护过程……地狱难度。追觅科技 追觅</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>69fc77ce000000002202799b</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc77ce000000002202799b?xsec_token=AB-w4DjPUYQJStSYryP2oTEiBKkMCRHoaHcDQ12QFHRU8=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看看我们雾化的效果。透明，量大、微米级够细，肉眼可见。追觅科技 追觅科技常新伟 </t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>69fc779e000000002301d565</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc779e000000002301d565?xsec_token=AB-w4DjPUYQJStSYryP2oTEqXDIk8vI8jGuelJvXzRclk=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>雾化精华模块，自带追觅精华，还能拆下来换你喜欢的任何精华。追觅科技 追觅科技常新</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>69fc7778000000002202a60b</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc7778000000002202a60b?xsec_token=AB-w4DjPUYQJStSYryP2oTEr0QKb3WHPgdB1EWxF8ze10=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>我们X30的吹风机上独有的雾化技术是微米级的！能让精华更快速更有效的到达目标区域</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>69fc774e000000001a02f4b7</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc774e000000001a02f4b7?xsec_token=AB-w4DjPUYQJStSYryP2oTEnSlDACDTXQrQQS7xfopzJw=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>今天拆箱一个X30吹风机给大家看看。追觅科技 追觅科技常新伟 追觅吹风机 追觅x</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>69fc7730000000001f003891</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc7730000000001f003891?xsec_token=AB-w4DjPUYQJStSYryP2oTElDAIdFjC8u_TfYO0qidgm0=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>扫地机、洗地机的业务月会，真的太无聊了追觅科技常新伟 追觅科技 追觅新品 追觅吹</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>69fc6fad000000003503a489</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc6fad000000003503a489?xsec_token=AB-w4DjPUYQJStSYryP2oTEhMzsATXXZTeKwDweQUPkac=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>开完我们的业务月会了，今天上午的月会是手机汽车大家电的月会，又是干劲满满的一个月</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>69fc1ab4000000003502176f</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fc1ab4000000003502176f?xsec_token=AB-w4DjPUYQJStSYryP2oTErdr6JvMdHLHuiiIAaoLq7A=</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="20" r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>常新伟</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>42248935879</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>追觅科技常新伟</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>692ef166000000003702bb39</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>都在问我头发怎么养护？既然你们诚心诚意地发问，我就严肃认真地回答。如果要保护头发</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>69fbece50000000035039f9f</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>19927</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>43506</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69fbece50000000035039f9f?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwsZ5NawPdlmNW8E6Y_o_2Y=</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/小红书笔记数据.xlsx
+++ b/小红书笔记数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="合并结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64134,7 +64134,7 @@
         </is>
       </c>
     </row>
-    <row r="1064">
+    <row customHeight="1" ht="20" r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64204,7 +64204,7 @@
         </is>
       </c>
     </row>
-    <row r="1065">
+    <row customHeight="1" ht="20" r="1065">
       <c r="A1065" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64270,7 +64270,7 @@
         </is>
       </c>
     </row>
-    <row r="1066">
+    <row customHeight="1" ht="20" r="1066">
       <c r="A1066" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64340,7 +64340,7 @@
         </is>
       </c>
     </row>
-    <row r="1067">
+    <row customHeight="1" ht="20" r="1067">
       <c r="A1067" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64410,7 +64410,7 @@
         </is>
       </c>
     </row>
-    <row r="1068">
+    <row customHeight="1" ht="20" r="1068">
       <c r="A1068" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64480,7 +64480,7 @@
         </is>
       </c>
     </row>
-    <row r="1069">
+    <row customHeight="1" ht="20" r="1069">
       <c r="A1069" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64562,7 +64562,7 @@
         </is>
       </c>
     </row>
-    <row r="1070">
+    <row customHeight="1" ht="20" r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64644,7 +64644,7 @@
         </is>
       </c>
     </row>
-    <row r="1071">
+    <row customHeight="1" ht="20" r="1071">
       <c r="A1071" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
     </row>
-    <row r="1072">
+    <row customHeight="1" ht="20" r="1072">
       <c r="A1072" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64808,7 +64808,7 @@
         </is>
       </c>
     </row>
-    <row r="1073">
+    <row customHeight="1" ht="20" r="1073">
       <c r="A1073" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64886,7 +64886,7 @@
         </is>
       </c>
     </row>
-    <row r="1074">
+    <row customHeight="1" ht="20" r="1074">
       <c r="A1074" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64960,7 +64960,7 @@
         </is>
       </c>
     </row>
-    <row r="1075">
+    <row customHeight="1" ht="20" r="1075">
       <c r="A1075" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65034,7 +65034,7 @@
         </is>
       </c>
     </row>
-    <row r="1076">
+    <row customHeight="1" ht="20" r="1076">
       <c r="A1076" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65108,7 +65108,7 @@
         </is>
       </c>
     </row>
-    <row r="1077">
+    <row customHeight="1" ht="20" r="1077">
       <c r="A1077" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
     </row>
-    <row r="1078">
+    <row customHeight="1" ht="20" r="1078">
       <c r="A1078" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65264,7 +65264,7 @@
         </is>
       </c>
     </row>
-    <row r="1079">
+    <row customHeight="1" ht="20" r="1079">
       <c r="A1079" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65330,7 +65330,7 @@
         </is>
       </c>
     </row>
-    <row r="1080">
+    <row customHeight="1" ht="20" r="1080">
       <c r="A1080" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65408,7 +65408,7 @@
         </is>
       </c>
     </row>
-    <row r="1081">
+    <row customHeight="1" ht="20" r="1081">
       <c r="A1081" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65490,7 +65490,7 @@
         </is>
       </c>
     </row>
-    <row r="1082">
+    <row customHeight="1" ht="20" r="1082">
       <c r="A1082" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65564,7 +65564,7 @@
         </is>
       </c>
     </row>
-    <row r="1083">
+    <row customHeight="1" ht="20" r="1083">
       <c r="A1083" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65642,7 +65642,7 @@
         </is>
       </c>
     </row>
-    <row r="1084">
+    <row customHeight="1" ht="20" r="1084">
       <c r="A1084" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65712,7 +65712,7 @@
         </is>
       </c>
     </row>
-    <row r="1085">
+    <row customHeight="1" ht="20" r="1085">
       <c r="A1085" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65778,7 +65778,7 @@
         </is>
       </c>
     </row>
-    <row r="1086">
+    <row customHeight="1" ht="20" r="1086">
       <c r="A1086" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65848,7 +65848,7 @@
         </is>
       </c>
     </row>
-    <row r="1087">
+    <row customHeight="1" ht="20" r="1087">
       <c r="A1087" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65926,7 +65926,7 @@
         </is>
       </c>
     </row>
-    <row r="1088">
+    <row customHeight="1" ht="20" r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65996,7 +65996,7 @@
         </is>
       </c>
     </row>
-    <row r="1089">
+    <row customHeight="1" ht="20" r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66062,7 +66062,7 @@
         </is>
       </c>
     </row>
-    <row r="1090">
+    <row customHeight="1" ht="20" r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66132,7 +66132,7 @@
         </is>
       </c>
     </row>
-    <row r="1091">
+    <row customHeight="1" ht="20" r="1091">
       <c r="A1091" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66206,7 +66206,7 @@
         </is>
       </c>
     </row>
-    <row r="1092">
+    <row customHeight="1" ht="20" r="1092">
       <c r="A1092" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66280,7 +66280,7 @@
         </is>
       </c>
     </row>
-    <row r="1093">
+    <row customHeight="1" ht="20" r="1093">
       <c r="A1093" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66354,7 +66354,7 @@
         </is>
       </c>
     </row>
-    <row r="1094">
+    <row customHeight="1" ht="20" r="1094">
       <c r="A1094" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66420,7 +66420,7 @@
         </is>
       </c>
     </row>
-    <row r="1095">
+    <row customHeight="1" ht="20" r="1095">
       <c r="A1095" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66486,7 +66486,7 @@
         </is>
       </c>
     </row>
-    <row r="1096">
+    <row customHeight="1" ht="20" r="1096">
       <c r="A1096" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66552,7 +66552,7 @@
         </is>
       </c>
     </row>
-    <row r="1097">
+    <row customHeight="1" ht="20" r="1097">
       <c r="A1097" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66634,7 +66634,7 @@
         </is>
       </c>
     </row>
-    <row r="1098">
+    <row customHeight="1" ht="20" r="1098">
       <c r="A1098" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66708,7 +66708,7 @@
         </is>
       </c>
     </row>
-    <row r="1099">
+    <row customHeight="1" ht="20" r="1099">
       <c r="A1099" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66774,7 +66774,7 @@
         </is>
       </c>
     </row>
-    <row r="1100">
+    <row customHeight="1" ht="20" r="1100">
       <c r="A1100" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66844,7 +66844,7 @@
         </is>
       </c>
     </row>
-    <row r="1101">
+    <row customHeight="1" ht="20" r="1101">
       <c r="A1101" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66914,7 +66914,7 @@
         </is>
       </c>
     </row>
-    <row r="1102">
+    <row customHeight="1" ht="20" r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66984,7 +66984,7 @@
         </is>
       </c>
     </row>
-    <row r="1103">
+    <row customHeight="1" ht="20" r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67054,7 +67054,7 @@
         </is>
       </c>
     </row>
-    <row r="1104">
+    <row customHeight="1" ht="20" r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67124,7 +67124,7 @@
         </is>
       </c>
     </row>
-    <row r="1105">
+    <row customHeight="1" ht="20" r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67194,7 +67194,7 @@
         </is>
       </c>
     </row>
-    <row r="1106">
+    <row customHeight="1" ht="20" r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67264,7 +67264,7 @@
         </is>
       </c>
     </row>
-    <row r="1107">
+    <row customHeight="1" ht="20" r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67334,7 +67334,7 @@
         </is>
       </c>
     </row>
-    <row r="1108">
+    <row customHeight="1" ht="20" r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67404,7 +67404,7 @@
         </is>
       </c>
     </row>
-    <row r="1109">
+    <row customHeight="1" ht="20" r="1109">
       <c r="A1109" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67474,7 +67474,7 @@
         </is>
       </c>
     </row>
-    <row r="1110">
+    <row customHeight="1" ht="20" r="1110">
       <c r="A1110" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67540,7 +67540,7 @@
         </is>
       </c>
     </row>
-    <row r="1111">
+    <row customHeight="1" ht="20" r="1111">
       <c r="A1111" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67610,7 +67610,7 @@
         </is>
       </c>
     </row>
-    <row r="1112">
+    <row customHeight="1" ht="20" r="1112">
       <c r="A1112" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67680,7 +67680,7 @@
         </is>
       </c>
     </row>
-    <row r="1113">
+    <row customHeight="1" ht="20" r="1113">
       <c r="A1113" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67750,7 +67750,7 @@
         </is>
       </c>
     </row>
-    <row r="1114">
+    <row customHeight="1" ht="20" r="1114">
       <c r="A1114" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
     </row>
-    <row r="1115">
+    <row customHeight="1" ht="20" r="1115">
       <c r="A1115" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67890,7 +67890,7 @@
         </is>
       </c>
     </row>
-    <row r="1116">
+    <row customHeight="1" ht="20" r="1116">
       <c r="A1116" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67960,7 +67960,7 @@
         </is>
       </c>
     </row>
-    <row r="1117">
+    <row customHeight="1" ht="20" r="1117">
       <c r="A1117" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -68030,7 +68030,7 @@
         </is>
       </c>
     </row>
-    <row r="1118">
+    <row customHeight="1" ht="20" r="1118">
       <c r="A1118" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -68100,7 +68100,7 @@
         </is>
       </c>
     </row>
-    <row r="1119">
+    <row customHeight="1" ht="20" r="1119">
       <c r="A1119" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68170,7 +68170,7 @@
         </is>
       </c>
     </row>
-    <row r="1120">
+    <row customHeight="1" ht="20" r="1120">
       <c r="A1120" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68240,7 +68240,7 @@
         </is>
       </c>
     </row>
-    <row r="1121">
+    <row customHeight="1" ht="20" r="1121">
       <c r="A1121" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68310,7 +68310,7 @@
         </is>
       </c>
     </row>
-    <row r="1122">
+    <row customHeight="1" ht="20" r="1122">
       <c r="A1122" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68380,7 +68380,7 @@
         </is>
       </c>
     </row>
-    <row r="1123">
+    <row customHeight="1" ht="20" r="1123">
       <c r="A1123" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68450,7 +68450,7 @@
         </is>
       </c>
     </row>
-    <row r="1124">
+    <row customHeight="1" ht="20" r="1124">
       <c r="A1124" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68520,7 +68520,7 @@
         </is>
       </c>
     </row>
-    <row r="1125">
+    <row customHeight="1" ht="20" r="1125">
       <c r="A1125" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68590,7 +68590,7 @@
         </is>
       </c>
     </row>
-    <row r="1126">
+    <row customHeight="1" ht="20" r="1126">
       <c r="A1126" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68660,7 +68660,7 @@
         </is>
       </c>
     </row>
-    <row r="1127">
+    <row customHeight="1" ht="20" r="1127">
       <c r="A1127" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68730,7 +68730,7 @@
         </is>
       </c>
     </row>
-    <row r="1128">
+    <row customHeight="1" ht="20" r="1128">
       <c r="A1128" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68800,7 +68800,7 @@
         </is>
       </c>
     </row>
-    <row r="1129">
+    <row customHeight="1" ht="20" r="1129">
       <c r="A1129" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68870,7 +68870,7 @@
         </is>
       </c>
     </row>
-    <row r="1130">
+    <row customHeight="1" ht="20" r="1130">
       <c r="A1130" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68940,7 +68940,7 @@
         </is>
       </c>
     </row>
-    <row r="1131">
+    <row customHeight="1" ht="20" r="1131">
       <c r="A1131" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69010,7 +69010,7 @@
         </is>
       </c>
     </row>
-    <row r="1132">
+    <row customHeight="1" ht="20" r="1132">
       <c r="A1132" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69080,7 +69080,7 @@
         </is>
       </c>
     </row>
-    <row r="1133">
+    <row customHeight="1" ht="20" r="1133">
       <c r="A1133" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69150,7 +69150,7 @@
         </is>
       </c>
     </row>
-    <row r="1134">
+    <row customHeight="1" ht="20" r="1134">
       <c r="A1134" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69220,7 +69220,7 @@
         </is>
       </c>
     </row>
-    <row r="1135">
+    <row customHeight="1" ht="20" r="1135">
       <c r="A1135" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69290,7 +69290,7 @@
         </is>
       </c>
     </row>
-    <row r="1136">
+    <row customHeight="1" ht="20" r="1136">
       <c r="A1136" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69360,7 +69360,7 @@
         </is>
       </c>
     </row>
-    <row r="1137">
+    <row customHeight="1" ht="20" r="1137">
       <c r="A1137" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69430,7 +69430,7 @@
         </is>
       </c>
     </row>
-    <row r="1138">
+    <row customHeight="1" ht="20" r="1138">
       <c r="A1138" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69500,7 +69500,7 @@
         </is>
       </c>
     </row>
-    <row r="1139">
+    <row customHeight="1" ht="20" r="1139">
       <c r="A1139" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69570,7 +69570,7 @@
         </is>
       </c>
     </row>
-    <row r="1140">
+    <row customHeight="1" ht="20" r="1140">
       <c r="A1140" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69640,7 +69640,7 @@
         </is>
       </c>
     </row>
-    <row r="1141">
+    <row customHeight="1" ht="20" r="1141">
       <c r="A1141" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69710,7 +69710,7 @@
         </is>
       </c>
     </row>
-    <row r="1142">
+    <row customHeight="1" ht="20" r="1142">
       <c r="A1142" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69780,7 +69780,7 @@
         </is>
       </c>
     </row>
-    <row r="1143">
+    <row customHeight="1" ht="20" r="1143">
       <c r="A1143" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69850,7 +69850,7 @@
         </is>
       </c>
     </row>
-    <row r="1144">
+    <row customHeight="1" ht="20" r="1144">
       <c r="A1144" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69920,7 +69920,7 @@
         </is>
       </c>
     </row>
-    <row r="1145">
+    <row customHeight="1" ht="20" r="1145">
       <c r="A1145" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69990,7 +69990,7 @@
         </is>
       </c>
     </row>
-    <row r="1146">
+    <row customHeight="1" ht="20" r="1146">
       <c r="A1146" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70060,7 +70060,7 @@
         </is>
       </c>
     </row>
-    <row r="1147">
+    <row customHeight="1" ht="20" r="1147">
       <c r="A1147" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70130,7 +70130,7 @@
         </is>
       </c>
     </row>
-    <row r="1148">
+    <row customHeight="1" ht="20" r="1148">
       <c r="A1148" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70200,7 +70200,7 @@
         </is>
       </c>
     </row>
-    <row r="1149">
+    <row customHeight="1" ht="20" r="1149">
       <c r="A1149" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70270,7 +70270,7 @@
         </is>
       </c>
     </row>
-    <row r="1150">
+    <row customHeight="1" ht="20" r="1150">
       <c r="A1150" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70340,7 +70340,7 @@
         </is>
       </c>
     </row>
-    <row r="1151">
+    <row customHeight="1" ht="20" r="1151">
       <c r="A1151" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70410,7 +70410,7 @@
         </is>
       </c>
     </row>
-    <row r="1152">
+    <row customHeight="1" ht="20" r="1152">
       <c r="A1152" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70480,7 +70480,7 @@
         </is>
       </c>
     </row>
-    <row r="1153">
+    <row customHeight="1" ht="20" r="1153">
       <c r="A1153" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70550,7 +70550,7 @@
         </is>
       </c>
     </row>
-    <row r="1154">
+    <row customHeight="1" ht="20" r="1154">
       <c r="A1154" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70620,7 +70620,7 @@
         </is>
       </c>
     </row>
-    <row r="1155">
+    <row customHeight="1" ht="20" r="1155">
       <c r="A1155" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70690,7 +70690,7 @@
         </is>
       </c>
     </row>
-    <row r="1156">
+    <row customHeight="1" ht="20" r="1156">
       <c r="A1156" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70760,7 +70760,7 @@
         </is>
       </c>
     </row>
-    <row r="1157">
+    <row customHeight="1" ht="20" r="1157">
       <c r="A1157" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70830,7 +70830,7 @@
         </is>
       </c>
     </row>
-    <row r="1158">
+    <row customHeight="1" ht="20" r="1158">
       <c r="A1158" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70900,7 +70900,7 @@
         </is>
       </c>
     </row>
-    <row r="1159">
+    <row customHeight="1" ht="20" r="1159">
       <c r="A1159" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70970,7 +70970,7 @@
         </is>
       </c>
     </row>
-    <row r="1160">
+    <row customHeight="1" ht="20" r="1160">
       <c r="A1160" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71040,7 +71040,7 @@
         </is>
       </c>
     </row>
-    <row r="1161">
+    <row customHeight="1" ht="20" r="1161">
       <c r="A1161" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71110,7 +71110,7 @@
         </is>
       </c>
     </row>
-    <row r="1162">
+    <row customHeight="1" ht="20" r="1162">
       <c r="A1162" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71180,7 +71180,7 @@
         </is>
       </c>
     </row>
-    <row r="1163">
+    <row customHeight="1" ht="20" r="1163">
       <c r="A1163" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71250,7 +71250,7 @@
         </is>
       </c>
     </row>
-    <row r="1164">
+    <row customHeight="1" ht="20" r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71320,7 +71320,7 @@
         </is>
       </c>
     </row>
-    <row r="1165">
+    <row customHeight="1" ht="20" r="1165">
       <c r="A1165" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71390,7 +71390,7 @@
         </is>
       </c>
     </row>
-    <row r="1166">
+    <row customHeight="1" ht="20" r="1166">
       <c r="A1166" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71460,7 +71460,7 @@
         </is>
       </c>
     </row>
-    <row r="1167">
+    <row customHeight="1" ht="20" r="1167">
       <c r="A1167" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71530,7 +71530,7 @@
         </is>
       </c>
     </row>
-    <row r="1168">
+    <row customHeight="1" ht="20" r="1168">
       <c r="A1168" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71600,7 +71600,7 @@
         </is>
       </c>
     </row>
-    <row r="1169">
+    <row customHeight="1" ht="20" r="1169">
       <c r="A1169" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71670,7 +71670,7 @@
         </is>
       </c>
     </row>
-    <row r="1170">
+    <row customHeight="1" ht="20" r="1170">
       <c r="A1170" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71740,7 +71740,7 @@
         </is>
       </c>
     </row>
-    <row r="1171">
+    <row customHeight="1" ht="20" r="1171">
       <c r="A1171" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71810,7 +71810,7 @@
         </is>
       </c>
     </row>
-    <row r="1172">
+    <row customHeight="1" ht="20" r="1172">
       <c r="A1172" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71880,7 +71880,7 @@
         </is>
       </c>
     </row>
-    <row r="1173">
+    <row customHeight="1" ht="20" r="1173">
       <c r="A1173" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71950,7 +71950,7 @@
         </is>
       </c>
     </row>
-    <row r="1174">
+    <row customHeight="1" ht="20" r="1174">
       <c r="A1174" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72020,7 +72020,7 @@
         </is>
       </c>
     </row>
-    <row r="1175">
+    <row customHeight="1" ht="20" r="1175">
       <c r="A1175" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72090,7 +72090,7 @@
         </is>
       </c>
     </row>
-    <row r="1176">
+    <row customHeight="1" ht="20" r="1176">
       <c r="A1176" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72160,7 +72160,7 @@
         </is>
       </c>
     </row>
-    <row r="1177">
+    <row customHeight="1" ht="20" r="1177">
       <c r="A1177" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72230,7 +72230,7 @@
         </is>
       </c>
     </row>
-    <row r="1178">
+    <row customHeight="1" ht="20" r="1178">
       <c r="A1178" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72300,7 +72300,7 @@
         </is>
       </c>
     </row>
-    <row r="1179">
+    <row customHeight="1" ht="20" r="1179">
       <c r="A1179" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72370,7 +72370,7 @@
         </is>
       </c>
     </row>
-    <row r="1180">
+    <row customHeight="1" ht="20" r="1180">
       <c r="A1180" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72440,7 +72440,7 @@
         </is>
       </c>
     </row>
-    <row r="1181">
+    <row customHeight="1" ht="20" r="1181">
       <c r="A1181" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72510,7 +72510,7 @@
         </is>
       </c>
     </row>
-    <row r="1182">
+    <row customHeight="1" ht="20" r="1182">
       <c r="A1182" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72580,7 +72580,7 @@
         </is>
       </c>
     </row>
-    <row r="1183">
+    <row customHeight="1" ht="20" r="1183">
       <c r="A1183" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72650,7 +72650,7 @@
         </is>
       </c>
     </row>
-    <row r="1184">
+    <row customHeight="1" ht="20" r="1184">
       <c r="A1184" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72720,7 +72720,7 @@
         </is>
       </c>
     </row>
-    <row r="1185">
+    <row customHeight="1" ht="20" r="1185">
       <c r="A1185" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72790,7 +72790,7 @@
         </is>
       </c>
     </row>
-    <row r="1186">
+    <row customHeight="1" ht="20" r="1186">
       <c r="A1186" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72860,7 +72860,7 @@
         </is>
       </c>
     </row>
-    <row r="1187">
+    <row customHeight="1" ht="20" r="1187">
       <c r="A1187" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -72930,7 +72930,7 @@
         </is>
       </c>
     </row>
-    <row r="1188">
+    <row customHeight="1" ht="20" r="1188">
       <c r="A1188" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73000,7 +73000,7 @@
         </is>
       </c>
     </row>
-    <row r="1189">
+    <row customHeight="1" ht="20" r="1189">
       <c r="A1189" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73070,7 +73070,7 @@
         </is>
       </c>
     </row>
-    <row r="1190">
+    <row customHeight="1" ht="20" r="1190">
       <c r="A1190" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73140,7 +73140,7 @@
         </is>
       </c>
     </row>
-    <row r="1191">
+    <row customHeight="1" ht="20" r="1191">
       <c r="A1191" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73210,7 +73210,7 @@
         </is>
       </c>
     </row>
-    <row r="1192">
+    <row customHeight="1" ht="20" r="1192">
       <c r="A1192" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73280,7 +73280,7 @@
         </is>
       </c>
     </row>
-    <row r="1193">
+    <row customHeight="1" ht="20" r="1193">
       <c r="A1193" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73350,7 +73350,7 @@
         </is>
       </c>
     </row>
-    <row r="1194">
+    <row customHeight="1" ht="20" r="1194">
       <c r="A1194" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73420,7 +73420,7 @@
         </is>
       </c>
     </row>
-    <row r="1195">
+    <row customHeight="1" ht="20" r="1195">
       <c r="A1195" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73490,7 +73490,7 @@
         </is>
       </c>
     </row>
-    <row r="1196">
+    <row customHeight="1" ht="20" r="1196">
       <c r="A1196" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73560,7 +73560,7 @@
         </is>
       </c>
     </row>
-    <row r="1197">
+    <row customHeight="1" ht="20" r="1197">
       <c r="A1197" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73630,7 +73630,7 @@
         </is>
       </c>
     </row>
-    <row r="1198">
+    <row customHeight="1" ht="20" r="1198">
       <c r="A1198" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73700,7 +73700,7 @@
         </is>
       </c>
     </row>
-    <row r="1199">
+    <row customHeight="1" ht="20" r="1199">
       <c r="A1199" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73770,7 +73770,7 @@
         </is>
       </c>
     </row>
-    <row r="1200">
+    <row customHeight="1" ht="20" r="1200">
       <c r="A1200" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73840,7 +73840,7 @@
         </is>
       </c>
     </row>
-    <row r="1201">
+    <row customHeight="1" ht="20" r="1201">
       <c r="A1201" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73910,7 +73910,7 @@
         </is>
       </c>
     </row>
-    <row r="1202">
+    <row customHeight="1" ht="20" r="1202">
       <c r="A1202" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73980,7 +73980,7 @@
         </is>
       </c>
     </row>
-    <row r="1203">
+    <row customHeight="1" ht="20" r="1203">
       <c r="A1203" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74046,7 +74046,7 @@
         </is>
       </c>
     </row>
-    <row r="1204">
+    <row customHeight="1" ht="20" r="1204">
       <c r="A1204" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74116,7 +74116,7 @@
         </is>
       </c>
     </row>
-    <row r="1205">
+    <row customHeight="1" ht="20" r="1205">
       <c r="A1205" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74186,7 +74186,7 @@
         </is>
       </c>
     </row>
-    <row r="1206">
+    <row customHeight="1" ht="20" r="1206">
       <c r="A1206" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74256,7 +74256,7 @@
         </is>
       </c>
     </row>
-    <row r="1207">
+    <row customHeight="1" ht="20" r="1207">
       <c r="A1207" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74326,7 +74326,7 @@
         </is>
       </c>
     </row>
-    <row r="1208">
+    <row customHeight="1" ht="20" r="1208">
       <c r="A1208" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74396,7 +74396,7 @@
         </is>
       </c>
     </row>
-    <row r="1209">
+    <row customHeight="1" ht="20" r="1209">
       <c r="A1209" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74466,7 +74466,7 @@
         </is>
       </c>
     </row>
-    <row r="1210">
+    <row customHeight="1" ht="20" r="1210">
       <c r="A1210" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74536,7 +74536,7 @@
         </is>
       </c>
     </row>
-    <row r="1211">
+    <row customHeight="1" ht="20" r="1211">
       <c r="A1211" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74606,7 +74606,7 @@
         </is>
       </c>
     </row>
-    <row r="1212">
+    <row customHeight="1" ht="20" r="1212">
       <c r="A1212" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74676,7 +74676,7 @@
         </is>
       </c>
     </row>
-    <row r="1213">
+    <row customHeight="1" ht="20" r="1213">
       <c r="A1213" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74746,7 +74746,7 @@
         </is>
       </c>
     </row>
-    <row r="1214">
+    <row customHeight="1" ht="20" r="1214">
       <c r="A1214" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74816,7 +74816,7 @@
         </is>
       </c>
     </row>
-    <row r="1215">
+    <row customHeight="1" ht="20" r="1215">
       <c r="A1215" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74886,7 +74886,7 @@
         </is>
       </c>
     </row>
-    <row r="1216">
+    <row customHeight="1" ht="20" r="1216">
       <c r="A1216" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74956,7 +74956,7 @@
         </is>
       </c>
     </row>
-    <row r="1217">
+    <row customHeight="1" ht="20" r="1217">
       <c r="A1217" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75026,7 +75026,7 @@
         </is>
       </c>
     </row>
-    <row r="1218">
+    <row customHeight="1" ht="20" r="1218">
       <c r="A1218" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75096,7 +75096,7 @@
         </is>
       </c>
     </row>
-    <row r="1219">
+    <row customHeight="1" ht="20" r="1219">
       <c r="A1219" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75166,7 +75166,7 @@
         </is>
       </c>
     </row>
-    <row r="1220">
+    <row customHeight="1" ht="20" r="1220">
       <c r="A1220" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75236,7 +75236,7 @@
         </is>
       </c>
     </row>
-    <row r="1221">
+    <row customHeight="1" ht="20" r="1221">
       <c r="A1221" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75306,7 +75306,7 @@
         </is>
       </c>
     </row>
-    <row r="1222">
+    <row customHeight="1" ht="20" r="1222">
       <c r="A1222" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75376,7 +75376,7 @@
         </is>
       </c>
     </row>
-    <row r="1223">
+    <row customHeight="1" ht="20" r="1223">
       <c r="A1223" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75446,7 +75446,7 @@
         </is>
       </c>
     </row>
-    <row r="1224">
+    <row customHeight="1" ht="20" r="1224">
       <c r="A1224" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75516,7 +75516,7 @@
         </is>
       </c>
     </row>
-    <row r="1225">
+    <row customHeight="1" ht="20" r="1225">
       <c r="A1225" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75586,7 +75586,7 @@
         </is>
       </c>
     </row>
-    <row r="1226">
+    <row customHeight="1" ht="20" r="1226">
       <c r="A1226" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75656,7 +75656,7 @@
         </is>
       </c>
     </row>
-    <row r="1227">
+    <row customHeight="1" ht="20" r="1227">
       <c r="A1227" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75726,7 +75726,7 @@
         </is>
       </c>
     </row>
-    <row r="1228">
+    <row customHeight="1" ht="20" r="1228">
       <c r="A1228" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75796,7 +75796,7 @@
         </is>
       </c>
     </row>
-    <row r="1229">
+    <row customHeight="1" ht="20" r="1229">
       <c r="A1229" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75866,7 +75866,7 @@
         </is>
       </c>
     </row>
-    <row r="1230">
+    <row customHeight="1" ht="20" r="1230">
       <c r="A1230" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -75936,7 +75936,7 @@
         </is>
       </c>
     </row>
-    <row r="1231">
+    <row customHeight="1" ht="20" r="1231">
       <c r="A1231" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76006,7 +76006,7 @@
         </is>
       </c>
     </row>
-    <row r="1232">
+    <row customHeight="1" ht="20" r="1232">
       <c r="A1232" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76076,7 +76076,7 @@
         </is>
       </c>
     </row>
-    <row r="1233">
+    <row customHeight="1" ht="20" r="1233">
       <c r="A1233" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76146,7 +76146,7 @@
         </is>
       </c>
     </row>
-    <row r="1234">
+    <row customHeight="1" ht="20" r="1234">
       <c r="A1234" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76216,7 +76216,7 @@
         </is>
       </c>
     </row>
-    <row r="1235">
+    <row customHeight="1" ht="20" r="1235">
       <c r="A1235" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76286,7 +76286,7 @@
         </is>
       </c>
     </row>
-    <row r="1236">
+    <row customHeight="1" ht="20" r="1236">
       <c r="A1236" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76356,7 +76356,7 @@
         </is>
       </c>
     </row>
-    <row r="1237">
+    <row customHeight="1" ht="20" r="1237">
       <c r="A1237" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76426,7 +76426,7 @@
         </is>
       </c>
     </row>
-    <row r="1238">
+    <row customHeight="1" ht="20" r="1238">
       <c r="A1238" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76496,7 +76496,7 @@
         </is>
       </c>
     </row>
-    <row r="1239">
+    <row customHeight="1" ht="20" r="1239">
       <c r="A1239" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76566,7 +76566,7 @@
         </is>
       </c>
     </row>
-    <row r="1240">
+    <row customHeight="1" ht="20" r="1240">
       <c r="A1240" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76636,7 +76636,7 @@
         </is>
       </c>
     </row>
-    <row r="1241">
+    <row customHeight="1" ht="20" r="1241">
       <c r="A1241" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76706,7 +76706,7 @@
         </is>
       </c>
     </row>
-    <row r="1242">
+    <row customHeight="1" ht="20" r="1242">
       <c r="A1242" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76776,7 +76776,7 @@
         </is>
       </c>
     </row>
-    <row r="1243">
+    <row customHeight="1" ht="20" r="1243">
       <c r="A1243" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76846,7 +76846,7 @@
         </is>
       </c>
     </row>
-    <row r="1244">
+    <row customHeight="1" ht="20" r="1244">
       <c r="A1244" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76916,7 +76916,7 @@
         </is>
       </c>
     </row>
-    <row r="1245">
+    <row customHeight="1" ht="20" r="1245">
       <c r="A1245" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76986,7 +76986,7 @@
         </is>
       </c>
     </row>
-    <row r="1246">
+    <row customHeight="1" ht="20" r="1246">
       <c r="A1246" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77056,7 +77056,7 @@
         </is>
       </c>
     </row>
-    <row r="1247">
+    <row customHeight="1" ht="20" r="1247">
       <c r="A1247" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77126,7 +77126,7 @@
         </is>
       </c>
     </row>
-    <row r="1248">
+    <row customHeight="1" ht="20" r="1248">
       <c r="A1248" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77196,7 +77196,7 @@
         </is>
       </c>
     </row>
-    <row r="1249">
+    <row customHeight="1" ht="20" r="1249">
       <c r="A1249" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77266,7 +77266,7 @@
         </is>
       </c>
     </row>
-    <row r="1250">
+    <row customHeight="1" ht="20" r="1250">
       <c r="A1250" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77336,7 +77336,7 @@
         </is>
       </c>
     </row>
-    <row r="1251">
+    <row customHeight="1" ht="20" r="1251">
       <c r="A1251" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77406,7 +77406,7 @@
         </is>
       </c>
     </row>
-    <row r="1252">
+    <row customHeight="1" ht="20" r="1252">
       <c r="A1252" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77476,7 +77476,7 @@
         </is>
       </c>
     </row>
-    <row r="1253">
+    <row customHeight="1" ht="20" r="1253">
       <c r="A1253" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77546,7 +77546,7 @@
         </is>
       </c>
     </row>
-    <row r="1254">
+    <row customHeight="1" ht="20" r="1254">
       <c r="A1254" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77616,7 +77616,7 @@
         </is>
       </c>
     </row>
-    <row r="1255">
+    <row customHeight="1" ht="20" r="1255">
       <c r="A1255" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77686,7 +77686,7 @@
         </is>
       </c>
     </row>
-    <row r="1256">
+    <row customHeight="1" ht="20" r="1256">
       <c r="A1256" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77756,7 +77756,7 @@
         </is>
       </c>
     </row>
-    <row r="1257">
+    <row customHeight="1" ht="20" r="1257">
       <c r="A1257" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77826,7 +77826,7 @@
         </is>
       </c>
     </row>
-    <row r="1258">
+    <row customHeight="1" ht="20" r="1258">
       <c r="A1258" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77896,7 +77896,7 @@
         </is>
       </c>
     </row>
-    <row r="1259">
+    <row customHeight="1" ht="20" r="1259">
       <c r="A1259" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77966,7 +77966,7 @@
         </is>
       </c>
     </row>
-    <row r="1260">
+    <row customHeight="1" ht="20" r="1260">
       <c r="A1260" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78036,7 +78036,7 @@
         </is>
       </c>
     </row>
-    <row r="1261">
+    <row customHeight="1" ht="20" r="1261">
       <c r="A1261" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78106,7 +78106,7 @@
         </is>
       </c>
     </row>
-    <row r="1262">
+    <row customHeight="1" ht="20" r="1262">
       <c r="A1262" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78176,7 +78176,7 @@
         </is>
       </c>
     </row>
-    <row r="1263">
+    <row customHeight="1" ht="20" r="1263">
       <c r="A1263" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78246,7 +78246,7 @@
         </is>
       </c>
     </row>
-    <row r="1264">
+    <row customHeight="1" ht="20" r="1264">
       <c r="A1264" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78316,7 +78316,7 @@
         </is>
       </c>
     </row>
-    <row r="1265">
+    <row customHeight="1" ht="20" r="1265">
       <c r="A1265" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78386,7 +78386,7 @@
         </is>
       </c>
     </row>
-    <row r="1266">
+    <row customHeight="1" ht="20" r="1266">
       <c r="A1266" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78456,7 +78456,7 @@
         </is>
       </c>
     </row>
-    <row r="1267">
+    <row customHeight="1" ht="20" r="1267">
       <c r="A1267" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78526,7 +78526,7 @@
         </is>
       </c>
     </row>
-    <row r="1268">
+    <row customHeight="1" ht="20" r="1268">
       <c r="A1268" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78596,7 +78596,7 @@
         </is>
       </c>
     </row>
-    <row r="1269">
+    <row customHeight="1" ht="20" r="1269">
       <c r="A1269" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78666,7 +78666,7 @@
         </is>
       </c>
     </row>
-    <row r="1270">
+    <row customHeight="1" ht="20" r="1270">
       <c r="A1270" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78736,7 +78736,7 @@
         </is>
       </c>
     </row>
-    <row r="1271">
+    <row customHeight="1" ht="20" r="1271">
       <c r="A1271" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78806,7 +78806,7 @@
         </is>
       </c>
     </row>
-    <row r="1272">
+    <row customHeight="1" ht="20" r="1272">
       <c r="A1272" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78876,7 +78876,7 @@
         </is>
       </c>
     </row>
-    <row r="1273">
+    <row customHeight="1" ht="20" r="1273">
       <c r="A1273" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78946,7 +78946,7 @@
         </is>
       </c>
     </row>
-    <row r="1274">
+    <row customHeight="1" ht="20" r="1274">
       <c r="A1274" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79012,7 +79012,7 @@
         </is>
       </c>
     </row>
-    <row r="1275">
+    <row customHeight="1" ht="20" r="1275">
       <c r="A1275" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79082,7 +79082,7 @@
         </is>
       </c>
     </row>
-    <row r="1276">
+    <row customHeight="1" ht="20" r="1276">
       <c r="A1276" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79152,7 +79152,7 @@
         </is>
       </c>
     </row>
-    <row r="1277">
+    <row customHeight="1" ht="20" r="1277">
       <c r="A1277" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79222,7 +79222,7 @@
         </is>
       </c>
     </row>
-    <row r="1278">
+    <row customHeight="1" ht="20" r="1278">
       <c r="A1278" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79292,7 +79292,7 @@
         </is>
       </c>
     </row>
-    <row r="1279">
+    <row customHeight="1" ht="20" r="1279">
       <c r="A1279" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79362,7 +79362,7 @@
         </is>
       </c>
     </row>
-    <row r="1280">
+    <row customHeight="1" ht="20" r="1280">
       <c r="A1280" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79432,7 +79432,7 @@
         </is>
       </c>
     </row>
-    <row r="1281">
+    <row customHeight="1" ht="20" r="1281">
       <c r="A1281" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79502,7 +79502,7 @@
         </is>
       </c>
     </row>
-    <row r="1282">
+    <row customHeight="1" ht="20" r="1282">
       <c r="A1282" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79572,7 +79572,7 @@
         </is>
       </c>
     </row>
-    <row r="1283">
+    <row customHeight="1" ht="20" r="1283">
       <c r="A1283" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79642,7 +79642,7 @@
         </is>
       </c>
     </row>
-    <row r="1284">
+    <row customHeight="1" ht="20" r="1284">
       <c r="A1284" s="2" t="inlineStr">
         <is>
           <t>王玉宝</t>
@@ -79712,7 +79712,7 @@
         </is>
       </c>
     </row>
-    <row r="1285">
+    <row customHeight="1" ht="20" r="1285">
       <c r="A1285" s="2" t="inlineStr">
         <is>
           <t>王玉宝</t>
@@ -79782,7 +79782,7 @@
         </is>
       </c>
     </row>
-    <row r="1286">
+    <row customHeight="1" ht="20" r="1286">
       <c r="A1286" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79852,7 +79852,7 @@
         </is>
       </c>
     </row>
-    <row r="1287">
+    <row customHeight="1" ht="20" r="1287">
       <c r="A1287" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79922,7 +79922,7 @@
         </is>
       </c>
     </row>
-    <row r="1288">
+    <row customHeight="1" ht="20" r="1288">
       <c r="A1288" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79992,7 +79992,7 @@
         </is>
       </c>
     </row>
-    <row r="1289">
+    <row customHeight="1" ht="20" r="1289">
       <c r="A1289" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80062,7 +80062,7 @@
         </is>
       </c>
     </row>
-    <row r="1290">
+    <row customHeight="1" ht="20" r="1290">
       <c r="A1290" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80132,7 +80132,7 @@
         </is>
       </c>
     </row>
-    <row r="1291">
+    <row customHeight="1" ht="20" r="1291">
       <c r="A1291" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80202,7 +80202,7 @@
         </is>
       </c>
     </row>
-    <row r="1292">
+    <row customHeight="1" ht="20" r="1292">
       <c r="A1292" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80272,7 +80272,7 @@
         </is>
       </c>
     </row>
-    <row r="1293">
+    <row customHeight="1" ht="20" r="1293">
       <c r="A1293" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80342,7 +80342,7 @@
         </is>
       </c>
     </row>
-    <row r="1294">
+    <row customHeight="1" ht="20" r="1294">
       <c r="A1294" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80412,7 +80412,7 @@
         </is>
       </c>
     </row>
-    <row r="1295">
+    <row customHeight="1" ht="20" r="1295">
       <c r="A1295" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80482,7 +80482,7 @@
         </is>
       </c>
     </row>
-    <row r="1296">
+    <row customHeight="1" ht="20" r="1296">
       <c r="A1296" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80552,7 +80552,7 @@
         </is>
       </c>
     </row>
-    <row r="1297">
+    <row customHeight="1" ht="20" r="1297">
       <c r="A1297" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80622,7 +80622,7 @@
         </is>
       </c>
     </row>
-    <row r="1298">
+    <row customHeight="1" ht="20" r="1298">
       <c r="A1298" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80692,7 +80692,7 @@
         </is>
       </c>
     </row>
-    <row r="1299">
+    <row customHeight="1" ht="20" r="1299">
       <c r="A1299" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80762,7 +80762,7 @@
         </is>
       </c>
     </row>
-    <row r="1300">
+    <row customHeight="1" ht="20" r="1300">
       <c r="A1300" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80832,7 +80832,7 @@
         </is>
       </c>
     </row>
-    <row r="1301">
+    <row customHeight="1" ht="20" r="1301">
       <c r="A1301" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80902,7 +80902,7 @@
         </is>
       </c>
     </row>
-    <row r="1302">
+    <row customHeight="1" ht="20" r="1302">
       <c r="A1302" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80972,7 +80972,7 @@
         </is>
       </c>
     </row>
-    <row r="1303">
+    <row customHeight="1" ht="20" r="1303">
       <c r="A1303" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81042,7 +81042,7 @@
         </is>
       </c>
     </row>
-    <row r="1304">
+    <row customHeight="1" ht="20" r="1304">
       <c r="A1304" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81112,7 +81112,7 @@
         </is>
       </c>
     </row>
-    <row r="1305">
+    <row customHeight="1" ht="20" r="1305">
       <c r="A1305" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81182,7 +81182,7 @@
         </is>
       </c>
     </row>
-    <row r="1306">
+    <row customHeight="1" ht="20" r="1306">
       <c r="A1306" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81252,7 +81252,7 @@
         </is>
       </c>
     </row>
-    <row r="1307">
+    <row customHeight="1" ht="20" r="1307">
       <c r="A1307" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81322,7 +81322,7 @@
         </is>
       </c>
     </row>
-    <row r="1308">
+    <row customHeight="1" ht="20" r="1308">
       <c r="A1308" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81392,7 +81392,7 @@
         </is>
       </c>
     </row>
-    <row r="1309">
+    <row customHeight="1" ht="20" r="1309">
       <c r="A1309" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81462,7 +81462,7 @@
         </is>
       </c>
     </row>
-    <row r="1310">
+    <row customHeight="1" ht="20" r="1310">
       <c r="A1310" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81532,7 +81532,7 @@
         </is>
       </c>
     </row>
-    <row r="1311">
+    <row customHeight="1" ht="20" r="1311">
       <c r="A1311" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81602,7 +81602,7 @@
         </is>
       </c>
     </row>
-    <row r="1312">
+    <row customHeight="1" ht="20" r="1312">
       <c r="A1312" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81672,7 +81672,7 @@
         </is>
       </c>
     </row>
-    <row r="1313">
+    <row customHeight="1" ht="20" r="1313">
       <c r="A1313" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81742,7 +81742,7 @@
         </is>
       </c>
     </row>
-    <row r="1314">
+    <row customHeight="1" ht="20" r="1314">
       <c r="A1314" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81812,7 +81812,7 @@
         </is>
       </c>
     </row>
-    <row r="1315">
+    <row customHeight="1" ht="20" r="1315">
       <c r="A1315" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81882,7 +81882,7 @@
         </is>
       </c>
     </row>
-    <row r="1316">
+    <row customHeight="1" ht="20" r="1316">
       <c r="A1316" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81952,7 +81952,7 @@
         </is>
       </c>
     </row>
-    <row r="1317">
+    <row customHeight="1" ht="20" r="1317">
       <c r="A1317" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82022,7 +82022,7 @@
         </is>
       </c>
     </row>
-    <row r="1318">
+    <row customHeight="1" ht="20" r="1318">
       <c r="A1318" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82092,7 +82092,7 @@
         </is>
       </c>
     </row>
-    <row r="1319">
+    <row customHeight="1" ht="20" r="1319">
       <c r="A1319" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82162,7 +82162,7 @@
         </is>
       </c>
     </row>
-    <row r="1320">
+    <row customHeight="1" ht="20" r="1320">
       <c r="A1320" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82232,7 +82232,7 @@
         </is>
       </c>
     </row>
-    <row r="1321">
+    <row customHeight="1" ht="20" r="1321">
       <c r="A1321" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82302,7 +82302,7 @@
         </is>
       </c>
     </row>
-    <row r="1322">
+    <row customHeight="1" ht="20" r="1322">
       <c r="A1322" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82372,7 +82372,7 @@
         </is>
       </c>
     </row>
-    <row r="1323">
+    <row customHeight="1" ht="20" r="1323">
       <c r="A1323" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82442,7 +82442,7 @@
         </is>
       </c>
     </row>
-    <row r="1324">
+    <row customHeight="1" ht="20" r="1324">
       <c r="A1324" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82512,7 +82512,7 @@
         </is>
       </c>
     </row>
-    <row r="1325">
+    <row customHeight="1" ht="20" r="1325">
       <c r="A1325" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82582,7 +82582,7 @@
         </is>
       </c>
     </row>
-    <row r="1326">
+    <row customHeight="1" ht="20" r="1326">
       <c r="A1326" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82652,7 +82652,7 @@
         </is>
       </c>
     </row>
-    <row r="1327">
+    <row customHeight="1" ht="20" r="1327">
       <c r="A1327" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82722,7 +82722,7 @@
         </is>
       </c>
     </row>
-    <row r="1328">
+    <row customHeight="1" ht="20" r="1328">
       <c r="A1328" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82792,7 +82792,7 @@
         </is>
       </c>
     </row>
-    <row r="1329">
+    <row customHeight="1" ht="20" r="1329">
       <c r="A1329" s="2" t="inlineStr">
         <is>
           <t>姚康</t>

--- a/小红书笔记数据.xlsx
+++ b/小红书笔记数据.xlsx
@@ -64134,7 +64134,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1064">
+    <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64204,7 +64204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1065">
+    <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64270,7 +64270,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1066">
+    <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64340,7 +64340,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1067">
+    <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64410,7 +64410,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1068">
+    <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64480,7 +64480,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1069">
+    <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64562,7 +64562,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1070">
+    <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64644,7 +64644,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1071">
+    <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1072">
+    <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64808,7 +64808,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1073">
+    <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64886,7 +64886,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1074">
+    <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -64960,7 +64960,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1075">
+    <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65034,7 +65034,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1076">
+    <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65108,7 +65108,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1077">
+    <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1078">
+    <row r="1078">
       <c r="A1078" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65264,7 +65264,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1079">
+    <row r="1079">
       <c r="A1079" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65330,7 +65330,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1080">
+    <row r="1080">
       <c r="A1080" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65408,7 +65408,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1081">
+    <row r="1081">
       <c r="A1081" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65490,7 +65490,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1082">
+    <row r="1082">
       <c r="A1082" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65564,7 +65564,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1083">
+    <row r="1083">
       <c r="A1083" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65642,7 +65642,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1084">
+    <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65712,7 +65712,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1085">
+    <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65778,7 +65778,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1086">
+    <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65848,7 +65848,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1087">
+    <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65926,7 +65926,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1088">
+    <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
           <t>文春艳</t>
@@ -65996,7 +65996,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1089">
+    <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66062,7 +66062,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1090">
+    <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66132,7 +66132,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1091">
+    <row r="1091">
       <c r="A1091" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66206,7 +66206,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1092">
+    <row r="1092">
       <c r="A1092" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66280,7 +66280,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1093">
+    <row r="1093">
       <c r="A1093" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66354,7 +66354,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1094">
+    <row r="1094">
       <c r="A1094" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66420,7 +66420,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1095">
+    <row r="1095">
       <c r="A1095" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66486,7 +66486,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1096">
+    <row r="1096">
       <c r="A1096" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66552,7 +66552,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1097">
+    <row r="1097">
       <c r="A1097" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66634,7 +66634,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1098">
+    <row r="1098">
       <c r="A1098" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66708,7 +66708,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1099">
+    <row r="1099">
       <c r="A1099" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66774,7 +66774,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1100">
+    <row r="1100">
       <c r="A1100" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66844,7 +66844,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1101">
+    <row r="1101">
       <c r="A1101" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66914,7 +66914,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1102">
+    <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -66984,7 +66984,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1103">
+    <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67054,7 +67054,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1104">
+    <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67124,7 +67124,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1105">
+    <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67194,7 +67194,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1106">
+    <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67264,7 +67264,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1107">
+    <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67334,7 +67334,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1108">
+    <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67404,7 +67404,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1109">
+    <row r="1109">
       <c r="A1109" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67474,7 +67474,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1110">
+    <row r="1110">
       <c r="A1110" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67540,7 +67540,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1111">
+    <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67610,7 +67610,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1112">
+    <row r="1112">
       <c r="A1112" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67680,7 +67680,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1113">
+    <row r="1113">
       <c r="A1113" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67750,7 +67750,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1114">
+    <row r="1114">
       <c r="A1114" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1115">
+    <row r="1115">
       <c r="A1115" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67890,7 +67890,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1116">
+    <row r="1116">
       <c r="A1116" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -67960,7 +67960,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1117">
+    <row r="1117">
       <c r="A1117" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -68030,7 +68030,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1118">
+    <row r="1118">
       <c r="A1118" s="2" t="inlineStr">
         <is>
           <t>朴钰宁</t>
@@ -68100,7 +68100,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1119">
+    <row r="1119">
       <c r="A1119" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68170,7 +68170,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1120">
+    <row r="1120">
       <c r="A1120" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68240,7 +68240,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1121">
+    <row r="1121">
       <c r="A1121" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68310,7 +68310,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1122">
+    <row r="1122">
       <c r="A1122" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68380,7 +68380,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1123">
+    <row r="1123">
       <c r="A1123" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68450,7 +68450,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1124">
+    <row r="1124">
       <c r="A1124" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68520,7 +68520,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1125">
+    <row r="1125">
       <c r="A1125" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68590,7 +68590,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1126">
+    <row r="1126">
       <c r="A1126" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68660,7 +68660,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1127">
+    <row r="1127">
       <c r="A1127" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68730,7 +68730,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1128">
+    <row r="1128">
       <c r="A1128" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68800,7 +68800,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1129">
+    <row r="1129">
       <c r="A1129" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68870,7 +68870,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1130">
+    <row r="1130">
       <c r="A1130" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -68940,7 +68940,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1131">
+    <row r="1131">
       <c r="A1131" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69010,7 +69010,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1132">
+    <row r="1132">
       <c r="A1132" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69080,7 +69080,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1133">
+    <row r="1133">
       <c r="A1133" s="2" t="inlineStr">
         <is>
           <t>董晓朦</t>
@@ -69150,7 +69150,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1134">
+    <row r="1134">
       <c r="A1134" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69220,7 +69220,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1135">
+    <row r="1135">
       <c r="A1135" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69290,7 +69290,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1136">
+    <row r="1136">
       <c r="A1136" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69360,7 +69360,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1137">
+    <row r="1137">
       <c r="A1137" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69430,7 +69430,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1138">
+    <row r="1138">
       <c r="A1138" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69500,7 +69500,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1139">
+    <row r="1139">
       <c r="A1139" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69570,7 +69570,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1140">
+    <row r="1140">
       <c r="A1140" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69640,7 +69640,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1141">
+    <row r="1141">
       <c r="A1141" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69710,7 +69710,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1142">
+    <row r="1142">
       <c r="A1142" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69780,7 +69780,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1143">
+    <row r="1143">
       <c r="A1143" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69850,7 +69850,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1144">
+    <row r="1144">
       <c r="A1144" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69920,7 +69920,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1145">
+    <row r="1145">
       <c r="A1145" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -69990,7 +69990,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1146">
+    <row r="1146">
       <c r="A1146" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70060,7 +70060,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1147">
+    <row r="1147">
       <c r="A1147" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70130,7 +70130,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1148">
+    <row r="1148">
       <c r="A1148" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70200,7 +70200,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1149">
+    <row r="1149">
       <c r="A1149" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70270,7 +70270,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1150">
+    <row r="1150">
       <c r="A1150" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70340,7 +70340,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1151">
+    <row r="1151">
       <c r="A1151" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70410,7 +70410,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1152">
+    <row r="1152">
       <c r="A1152" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70480,7 +70480,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1153">
+    <row r="1153">
       <c r="A1153" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70550,7 +70550,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1154">
+    <row r="1154">
       <c r="A1154" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70620,7 +70620,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1155">
+    <row r="1155">
       <c r="A1155" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70690,7 +70690,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1156">
+    <row r="1156">
       <c r="A1156" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70760,7 +70760,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1157">
+    <row r="1157">
       <c r="A1157" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70830,7 +70830,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1158">
+    <row r="1158">
       <c r="A1158" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70900,7 +70900,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1159">
+    <row r="1159">
       <c r="A1159" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -70970,7 +70970,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1160">
+    <row r="1160">
       <c r="A1160" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71040,7 +71040,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1161">
+    <row r="1161">
       <c r="A1161" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71110,7 +71110,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1162">
+    <row r="1162">
       <c r="A1162" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71180,7 +71180,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1163">
+    <row r="1163">
       <c r="A1163" s="2" t="inlineStr">
         <is>
           <t>陈俊男</t>
@@ -71250,7 +71250,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1164">
+    <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71320,7 +71320,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1165">
+    <row r="1165">
       <c r="A1165" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71390,7 +71390,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1166">
+    <row r="1166">
       <c r="A1166" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71460,7 +71460,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1167">
+    <row r="1167">
       <c r="A1167" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71530,7 +71530,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1168">
+    <row r="1168">
       <c r="A1168" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71600,7 +71600,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1169">
+    <row r="1169">
       <c r="A1169" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71670,7 +71670,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1170">
+    <row r="1170">
       <c r="A1170" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71740,7 +71740,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1171">
+    <row r="1171">
       <c r="A1171" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71810,7 +71810,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1172">
+    <row r="1172">
       <c r="A1172" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71880,7 +71880,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1173">
+    <row r="1173">
       <c r="A1173" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -71950,7 +71950,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1174">
+    <row r="1174">
       <c r="A1174" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72020,7 +72020,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1175">
+    <row r="1175">
       <c r="A1175" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72090,7 +72090,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1176">
+    <row r="1176">
       <c r="A1176" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72160,7 +72160,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1177">
+    <row r="1177">
       <c r="A1177" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72230,7 +72230,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1178">
+    <row r="1178">
       <c r="A1178" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72300,7 +72300,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1179">
+    <row r="1179">
       <c r="A1179" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72370,7 +72370,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1180">
+    <row r="1180">
       <c r="A1180" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72440,7 +72440,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1181">
+    <row r="1181">
       <c r="A1181" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72510,7 +72510,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1182">
+    <row r="1182">
       <c r="A1182" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72580,7 +72580,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1183">
+    <row r="1183">
       <c r="A1183" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72650,7 +72650,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1184">
+    <row r="1184">
       <c r="A1184" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72720,7 +72720,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1185">
+    <row r="1185">
       <c r="A1185" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72790,7 +72790,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1186">
+    <row r="1186">
       <c r="A1186" s="2" t="inlineStr">
         <is>
           <t>——</t>
@@ -72860,7 +72860,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1187">
+    <row r="1187">
       <c r="A1187" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -72930,7 +72930,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1188">
+    <row r="1188">
       <c r="A1188" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73000,7 +73000,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1189">
+    <row r="1189">
       <c r="A1189" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73070,7 +73070,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1190">
+    <row r="1190">
       <c r="A1190" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73140,7 +73140,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1191">
+    <row r="1191">
       <c r="A1191" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73210,7 +73210,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1192">
+    <row r="1192">
       <c r="A1192" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73280,7 +73280,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1193">
+    <row r="1193">
       <c r="A1193" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73350,7 +73350,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1194">
+    <row r="1194">
       <c r="A1194" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73420,7 +73420,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1195">
+    <row r="1195">
       <c r="A1195" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73490,7 +73490,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1196">
+    <row r="1196">
       <c r="A1196" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73560,7 +73560,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1197">
+    <row r="1197">
       <c r="A1197" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73630,7 +73630,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1198">
+    <row r="1198">
       <c r="A1198" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73700,7 +73700,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1199">
+    <row r="1199">
       <c r="A1199" s="2" t="inlineStr">
         <is>
           <t>黄国伟</t>
@@ -73770,7 +73770,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1200">
+    <row r="1200">
       <c r="A1200" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73840,7 +73840,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1201">
+    <row r="1201">
       <c r="A1201" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73910,7 +73910,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1202">
+    <row r="1202">
       <c r="A1202" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -73980,7 +73980,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1203">
+    <row r="1203">
       <c r="A1203" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74046,7 +74046,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1204">
+    <row r="1204">
       <c r="A1204" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74116,7 +74116,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1205">
+    <row r="1205">
       <c r="A1205" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74186,7 +74186,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1206">
+    <row r="1206">
       <c r="A1206" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74256,7 +74256,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1207">
+    <row r="1207">
       <c r="A1207" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74326,7 +74326,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1208">
+    <row r="1208">
       <c r="A1208" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74396,7 +74396,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1209">
+    <row r="1209">
       <c r="A1209" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74466,7 +74466,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1210">
+    <row r="1210">
       <c r="A1210" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74536,7 +74536,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1211">
+    <row r="1211">
       <c r="A1211" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74606,7 +74606,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1212">
+    <row r="1212">
       <c r="A1212" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74676,7 +74676,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1213">
+    <row r="1213">
       <c r="A1213" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74746,7 +74746,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1214">
+    <row r="1214">
       <c r="A1214" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74816,7 +74816,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1215">
+    <row r="1215">
       <c r="A1215" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74886,7 +74886,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1216">
+    <row r="1216">
       <c r="A1216" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -74956,7 +74956,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1217">
+    <row r="1217">
       <c r="A1217" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75026,7 +75026,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1218">
+    <row r="1218">
       <c r="A1218" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75096,7 +75096,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1219">
+    <row r="1219">
       <c r="A1219" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75166,7 +75166,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1220">
+    <row r="1220">
       <c r="A1220" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75236,7 +75236,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1221">
+    <row r="1221">
       <c r="A1221" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75306,7 +75306,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1222">
+    <row r="1222">
       <c r="A1222" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75376,7 +75376,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1223">
+    <row r="1223">
       <c r="A1223" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75446,7 +75446,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1224">
+    <row r="1224">
       <c r="A1224" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75516,7 +75516,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1225">
+    <row r="1225">
       <c r="A1225" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75586,7 +75586,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1226">
+    <row r="1226">
       <c r="A1226" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75656,7 +75656,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1227">
+    <row r="1227">
       <c r="A1227" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75726,7 +75726,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1228">
+    <row r="1228">
       <c r="A1228" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75796,7 +75796,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1229">
+    <row r="1229">
       <c r="A1229" s="2" t="inlineStr">
         <is>
           <t>高争光</t>
@@ -75866,7 +75866,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1230">
+    <row r="1230">
       <c r="A1230" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -75936,7 +75936,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1231">
+    <row r="1231">
       <c r="A1231" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76006,7 +76006,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1232">
+    <row r="1232">
       <c r="A1232" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76076,7 +76076,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1233">
+    <row r="1233">
       <c r="A1233" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76146,7 +76146,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1234">
+    <row r="1234">
       <c r="A1234" s="2" t="inlineStr">
         <is>
           <t>赵虹圳</t>
@@ -76216,7 +76216,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1235">
+    <row r="1235">
       <c r="A1235" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76286,7 +76286,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1236">
+    <row r="1236">
       <c r="A1236" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76356,7 +76356,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1237">
+    <row r="1237">
       <c r="A1237" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76426,7 +76426,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1238">
+    <row r="1238">
       <c r="A1238" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76496,7 +76496,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1239">
+    <row r="1239">
       <c r="A1239" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76566,7 +76566,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1240">
+    <row r="1240">
       <c r="A1240" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76636,7 +76636,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1241">
+    <row r="1241">
       <c r="A1241" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76706,7 +76706,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1242">
+    <row r="1242">
       <c r="A1242" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76776,7 +76776,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1243">
+    <row r="1243">
       <c r="A1243" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76846,7 +76846,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1244">
+    <row r="1244">
       <c r="A1244" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76916,7 +76916,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1245">
+    <row r="1245">
       <c r="A1245" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -76986,7 +76986,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1246">
+    <row r="1246">
       <c r="A1246" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77056,7 +77056,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1247">
+    <row r="1247">
       <c r="A1247" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77126,7 +77126,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1248">
+    <row r="1248">
       <c r="A1248" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77196,7 +77196,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1249">
+    <row r="1249">
       <c r="A1249" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77266,7 +77266,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1250">
+    <row r="1250">
       <c r="A1250" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77336,7 +77336,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1251">
+    <row r="1251">
       <c r="A1251" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77406,7 +77406,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1252">
+    <row r="1252">
       <c r="A1252" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77476,7 +77476,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1253">
+    <row r="1253">
       <c r="A1253" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77546,7 +77546,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1254">
+    <row r="1254">
       <c r="A1254" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77616,7 +77616,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1255">
+    <row r="1255">
       <c r="A1255" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77686,7 +77686,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1256">
+    <row r="1256">
       <c r="A1256" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77756,7 +77756,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1257">
+    <row r="1257">
       <c r="A1257" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77826,7 +77826,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1258">
+    <row r="1258">
       <c r="A1258" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77896,7 +77896,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1259">
+    <row r="1259">
       <c r="A1259" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -77966,7 +77966,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1260">
+    <row r="1260">
       <c r="A1260" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78036,7 +78036,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1261">
+    <row r="1261">
       <c r="A1261" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78106,7 +78106,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1262">
+    <row r="1262">
       <c r="A1262" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78176,7 +78176,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1263">
+    <row r="1263">
       <c r="A1263" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78246,7 +78246,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1264">
+    <row r="1264">
       <c r="A1264" s="2" t="inlineStr">
         <is>
           <t>郭世雷</t>
@@ -78316,7 +78316,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1265">
+    <row r="1265">
       <c r="A1265" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78386,7 +78386,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1266">
+    <row r="1266">
       <c r="A1266" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78456,7 +78456,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1267">
+    <row r="1267">
       <c r="A1267" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78526,7 +78526,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1268">
+    <row r="1268">
       <c r="A1268" s="2" t="inlineStr">
         <is>
           <t>张祺</t>
@@ -78596,7 +78596,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1269">
+    <row r="1269">
       <c r="A1269" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78666,7 +78666,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1270">
+    <row r="1270">
       <c r="A1270" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78736,7 +78736,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1271">
+    <row r="1271">
       <c r="A1271" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78806,7 +78806,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1272">
+    <row r="1272">
       <c r="A1272" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78876,7 +78876,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1273">
+    <row r="1273">
       <c r="A1273" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -78946,7 +78946,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1274">
+    <row r="1274">
       <c r="A1274" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79012,7 +79012,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1275">
+    <row r="1275">
       <c r="A1275" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79082,7 +79082,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1276">
+    <row r="1276">
       <c r="A1276" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79152,7 +79152,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1277">
+    <row r="1277">
       <c r="A1277" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79222,7 +79222,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1278">
+    <row r="1278">
       <c r="A1278" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79292,7 +79292,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1279">
+    <row r="1279">
       <c r="A1279" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79362,7 +79362,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1280">
+    <row r="1280">
       <c r="A1280" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79432,7 +79432,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1281">
+    <row r="1281">
       <c r="A1281" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79502,7 +79502,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1282">
+    <row r="1282">
       <c r="A1282" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79572,7 +79572,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1283">
+    <row r="1283">
       <c r="A1283" s="2" t="inlineStr">
         <is>
           <t>王星</t>
@@ -79642,7 +79642,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1284">
+    <row r="1284">
       <c r="A1284" s="2" t="inlineStr">
         <is>
           <t>王玉宝</t>
@@ -79712,7 +79712,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1285">
+    <row r="1285">
       <c r="A1285" s="2" t="inlineStr">
         <is>
           <t>王玉宝</t>
@@ -79782,7 +79782,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1286">
+    <row r="1286">
       <c r="A1286" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79852,7 +79852,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1287">
+    <row r="1287">
       <c r="A1287" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79922,7 +79922,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1288">
+    <row r="1288">
       <c r="A1288" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -79992,7 +79992,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1289">
+    <row r="1289">
       <c r="A1289" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80062,7 +80062,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1290">
+    <row r="1290">
       <c r="A1290" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80132,7 +80132,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1291">
+    <row r="1291">
       <c r="A1291" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80202,7 +80202,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1292">
+    <row r="1292">
       <c r="A1292" s="2" t="inlineStr">
         <is>
           <t>杨大娜</t>
@@ -80272,7 +80272,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1293">
+    <row r="1293">
       <c r="A1293" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80342,7 +80342,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1294">
+    <row r="1294">
       <c r="A1294" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80412,7 +80412,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1295">
+    <row r="1295">
       <c r="A1295" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80482,7 +80482,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1296">
+    <row r="1296">
       <c r="A1296" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80552,7 +80552,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1297">
+    <row r="1297">
       <c r="A1297" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80622,7 +80622,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1298">
+    <row r="1298">
       <c r="A1298" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80692,7 +80692,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1299">
+    <row r="1299">
       <c r="A1299" s="2" t="inlineStr">
         <is>
           <t>姚亚俊</t>
@@ -80762,7 +80762,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1300">
+    <row r="1300">
       <c r="A1300" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80832,7 +80832,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1301">
+    <row r="1301">
       <c r="A1301" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80902,7 +80902,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1302">
+    <row r="1302">
       <c r="A1302" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -80972,7 +80972,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1303">
+    <row r="1303">
       <c r="A1303" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81042,7 +81042,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1304">
+    <row r="1304">
       <c r="A1304" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81112,7 +81112,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1305">
+    <row r="1305">
       <c r="A1305" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81182,7 +81182,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1306">
+    <row r="1306">
       <c r="A1306" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81252,7 +81252,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1307">
+    <row r="1307">
       <c r="A1307" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81322,7 +81322,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1308">
+    <row r="1308">
       <c r="A1308" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81392,7 +81392,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1309">
+    <row r="1309">
       <c r="A1309" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81462,7 +81462,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1310">
+    <row r="1310">
       <c r="A1310" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81532,7 +81532,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1311">
+    <row r="1311">
       <c r="A1311" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81602,7 +81602,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1312">
+    <row r="1312">
       <c r="A1312" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81672,7 +81672,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1313">
+    <row r="1313">
       <c r="A1313" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81742,7 +81742,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1314">
+    <row r="1314">
       <c r="A1314" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81812,7 +81812,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1315">
+    <row r="1315">
       <c r="A1315" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81882,7 +81882,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1316">
+    <row r="1316">
       <c r="A1316" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -81952,7 +81952,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1317">
+    <row r="1317">
       <c r="A1317" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82022,7 +82022,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1318">
+    <row r="1318">
       <c r="A1318" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82092,7 +82092,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1319">
+    <row r="1319">
       <c r="A1319" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82162,7 +82162,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1320">
+    <row r="1320">
       <c r="A1320" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82232,7 +82232,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1321">
+    <row r="1321">
       <c r="A1321" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82302,7 +82302,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1322">
+    <row r="1322">
       <c r="A1322" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82372,7 +82372,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1323">
+    <row r="1323">
       <c r="A1323" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82442,7 +82442,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1324">
+    <row r="1324">
       <c r="A1324" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82512,7 +82512,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1325">
+    <row r="1325">
       <c r="A1325" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82582,7 +82582,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1326">
+    <row r="1326">
       <c r="A1326" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82652,7 +82652,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1327">
+    <row r="1327">
       <c r="A1327" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82722,7 +82722,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1328">
+    <row r="1328">
       <c r="A1328" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
@@ -82792,7 +82792,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="20" r="1329">
+    <row r="1329">
       <c r="A1329" s="2" t="inlineStr">
         <is>
           <t>姚康</t>
